--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -488,6 +488,15 @@
   </si>
   <si>
     <t xml:space="preserve">El propio sistema de autenticación de Supabase permite enviar automáticamente el correo de bienvenida con el enlace para que el empleado configure su contraseña, sin necesidad de contratar un servicio de correo por separado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login por usuario+contraseña (resuelve usuario a email y usa Supabase Auth). Falta correr supabase/migrations/0001_init.sql en el proyecto real para probarlo en vivo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mismo login que RF-01; el middleware redirige a /admin cuando el rol es dueño. Falta correr la migración SQL para probarlo en vivo.</t>
   </si>
 </sst>
 </file>
@@ -1030,9 +1039,11 @@
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
@@ -1051,9 +1062,11 @@
         <v>16</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="4"/>
+        <v>154</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -497,6 +497,21 @@
   </si>
   <si>
     <t xml:space="preserve">Mismo login que RF-01; el middleware redirige a /admin cuando el rol es dueño. Falta correr la migración SQL para probarlo en vivo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alta/edición/desactivación de empleados en /admin/empleados. Falta correr la migración SQL para probar en vivo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lib/username.ts genera el usuario (primera letra + apellido, sin acentos) con desambiguación por colisión. Cubierto por tests unitarios.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al crear el empleado se invita por correo con supabase.auth.admin.inviteUserByEmail. Falta probarlo con el proyecto real.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/set-password permite al empleado definir su contraseña vía el enlace de invitación; el dueño nunca la ve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Botón "Reenviar invitación" en /admin/empleados/[id].</t>
   </si>
 </sst>
 </file>
@@ -1190,9 +1205,11 @@
         <v>16</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="4"/>
+        <v>154</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
@@ -1463,9 +1480,11 @@
         <v>24</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
@@ -1484,9 +1503,11 @@
         <v>24</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="4"/>
+        <v>154</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
@@ -1505,9 +1526,11 @@
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
@@ -1526,9 +1549,11 @@
         <v>16</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="4"/>
+        <v>154</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>161</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G25"/>

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -512,6 +512,12 @@
   </si>
   <si>
     <t xml:space="preserve">Botón "Reenviar invitación" en /admin/empleados/[id].</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El home del empleado muestra el horario acordado de la semana en curso (solo informativo).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/admin/empleados/[id]/horario: editor por semana (lunes a domingo) con total de horas sugerido en vivo, navegación entre semanas y horario por defecto reutilizable.</t>
   </si>
 </sst>
 </file>
@@ -1184,9 +1190,11 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
@@ -1228,9 +1236,11 @@
         <v>16</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -518,6 +518,9 @@
   </si>
   <si>
     <t xml:space="preserve">/admin/empleados/[id]/horario: editor por semana (lunes a domingo) con total de horas sugerido en vivo, navegación entre semanas y horario por defecto reutilizable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/admin/qr genera, descarga y regenera el QR maestro (invalida el anterior y deja auditoría). Falta correr la migración SQL para probarlo en vivo.</t>
   </si>
 </sst>
 </file>
@@ -1427,9 +1430,11 @@
         <v>67</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="4"/>
+        <v>154</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -521,6 +521,15 @@
   </si>
   <si>
     <t xml:space="preserve">/admin/qr genera, descarga y regenera el QR maestro (invalida el anterior y deja auditoría). Falta correr la migración SQL para probarlo en vivo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/marcar activa la cámara (html5-qrcode), valida el QR contra el token activo y registra la marca en /api/time-entries/mark. Falta correr la migración SQL para probarlo en vivo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lib/attendance/pairing.ts determina entrada/salida según las marcas del día (con tests unitarios).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home del empleado: marcas del día y total (lib/attendance/daily.ts).</t>
   </si>
 </sst>
 </file>
@@ -1109,9 +1118,11 @@
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
@@ -1130,9 +1141,11 @@
         <v>24</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="4"/>
+        <v>154</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -1151,9 +1164,11 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -530,6 +530,15 @@
   </si>
   <si>
     <t xml:space="preserve">Home del empleado: marcas del día y total (lib/attendance/daily.ts).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home del empleado muestra pactadas, trabajadas, ajustes y saldo de la semana en curso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lib/attendance/pairing.ts suma los tramos del día al minuto exacto (sin redondeo).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lib/attendance/balance.ts calcula el saldo semanal (pactadas - trabajadas + ajustes) en tiempo real, con tests unitarios.</t>
   </si>
 </sst>
 </file>
@@ -1187,9 +1196,11 @@
         <v>11</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="4"/>
+        <v>154</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
@@ -1340,9 +1351,11 @@
         <v>24</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -1361,9 +1374,11 @@
         <v>24</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="4"/>
+        <v>154</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -539,6 +539,21 @@
   </si>
   <si>
     <t xml:space="preserve">lib/attendance/balance.ts calcula el saldo semanal (pactadas - trabajadas + ajustes) en tiempo real, con tests unitarios.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/admin/marcas: listado filtrable por empleado y rango de fechas, agrupado por día.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días pasados con una entrada sin salida se marcan "Pendiente de revisión" (no se contabilizan hasta corregirse).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edición inline (tipo/hora/nota), eliminación y alta manual de marcas, todas identificadas como manuales en el historial.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El mismo panel de marcas permite elegir cualquier rango de fechas pasado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toda alta/edición/borrado manual de marcas queda en audit_log (lib/audit.ts) con actor, valor anterior y nuevo.</t>
   </si>
 </sst>
 </file>
@@ -1288,9 +1303,11 @@
         <v>16</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="4"/>
+        <v>154</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
@@ -1309,9 +1326,11 @@
         <v>24</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
@@ -1330,9 +1349,11 @@
         <v>16</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="4"/>
+        <v>154</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
@@ -1439,9 +1460,11 @@
         <v>16</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
@@ -1483,9 +1506,11 @@
         <v>24</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -554,6 +554,9 @@
   </si>
   <si>
     <t xml:space="preserve">Toda alta/edición/borrado manual de marcas queda en audit_log (lib/audit.ts) con actor, valor anterior y nuevo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/admin/ajustes: alta (empleado, semana, horas +/-, concepto libre) y eliminación, ya integrado al cálculo de saldo semanal. Falta correr la migración SQL para probarlo en vivo.</t>
   </si>
 </sst>
 </file>
@@ -1418,9 +1421,11 @@
         <v>16</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -557,6 +557,9 @@
   </si>
   <si>
     <t xml:space="preserve">/admin/ajustes: alta (empleado, semana, horas +/-, concepto libre) y eliminación, ya integrado al cálculo de saldo semanal. Falta correr la migración SQL para probarlo en vivo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/admin/reportes + /api/reports/monthly genera un .xlsx (consolidado + una hoja por empleado) con horas, saldos semanales, ajustes y totales del mes. PDF queda como mejora futura. Falta correr la migración SQL para probarlo en vivo.</t>
   </si>
 </sst>
 </file>
@@ -1444,9 +1447,11 @@
         <v>16</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="4"/>
+        <v>154</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -560,6 +560,24 @@
   </si>
   <si>
     <t xml:space="preserve">/admin/reportes + /api/reports/monthly genera un .xlsx (consolidado + una hoja por empleado) con horas, saldos semanales, ajustes y totales del mes. PDF queda como mejora futura. Falta correr la migración SQL para probarlo en vivo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo en un navegador real contra el proyecto de Supabase: login por usuario/contraseña funciona de punta a punta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo: login del dueño redirige correctamente a /admin según el rol.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo desde la app real: alta de empleado, generación de usuario e invitación por correo confirmadas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo: username generado automáticamente al dar de alta un empleado real.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo: el correo de invitación llegó correctamente a la casilla del empleado de prueba.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo tras corregir un bug real (el proyecto usa flujo implícito de Supabase Auth, no PKCE): el empleado ya puede definir su contraseña desde el enlace del correo.</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1123,7 @@
         <v>154</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1128,7 +1146,7 @@
         <v>154</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1266,7 +1284,7 @@
         <v>154</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1563,7 +1581,7 @@
         <v>154</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1586,7 +1604,7 @@
         <v>154</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1609,7 +1627,7 @@
         <v>154</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -578,6 +578,33 @@
   </si>
   <si>
     <t xml:space="preserve">Verificado en vivo tras corregir un bug real (el proyecto usa flujo implícito de Supabase Auth, no PKCE): el empleado ya puede definir su contraseña desde el enlace del correo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo con marca manual: detecta correctamente el próximo tipo (entrada/salida).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo: el empleado de prueba ve sus marcas del día.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo: saldo semanal correcto (pactadas/trabajadas/ajuste) con datos reales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo: las marcas aparecen en /admin/marcas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo: alta manual de entrada/salida funciona correctamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo con datos reales, además de tests unitarios.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo: ajuste de horas reflejado correctamente en el saldo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se encontró y corrigió un bug real en vivo: el reporte no mostraba horas trabajadas/ajustes de la semana en curso cuando su lunes caía en el mes anterior. Corregido incluyendo semanas superpuestas al mes. Ver ESTADO_PRUEBAS.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo: se ve el QR y se descarga correctamente. Falta probar el botón de regenerar.</t>
   </si>
 </sst>
 </file>
@@ -1192,7 +1219,7 @@
         <v>154</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1215,7 +1242,7 @@
         <v>154</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1238,7 +1265,7 @@
         <v>154</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1330,7 +1357,7 @@
         <v>154</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1376,7 +1403,7 @@
         <v>154</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1399,7 +1426,7 @@
         <v>154</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1422,7 +1449,7 @@
         <v>154</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1445,7 +1472,7 @@
         <v>154</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1468,7 +1495,7 @@
         <v>154</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1514,7 +1541,7 @@
         <v>154</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -605,6 +605,9 @@
   </si>
   <si>
     <t xml:space="preserve">Verificado en vivo: se ve el QR y se descarga correctamente. Falta probar el botón de regenerar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo tras corregir el bug de semanas superpuestas: el reporte de julio ya muestra correctamente las horas trabajadas y el ajuste de Ana. Ver ESTADO_PRUEBAS.md.</t>
   </si>
 </sst>
 </file>
@@ -1495,7 +1498,7 @@
         <v>154</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -608,6 +608,21 @@
   </si>
   <si>
     <t xml:space="preserve">Verificado en vivo tras corregir el bug de semanas superpuestas: el reporte de julio ya muestra correctamente las horas trabajadas y el ajuste de Ana. Ver ESTADO_PRUEBAS.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo: el empleado ve el horario acordado actualizado en su home.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se encontró y corrigió un bug real en vivo: el editor conservaba datos de la semana/empleado anterior al navegar. Ver ESTADO_PRUEBAS.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo: el cartel de pendiente de revisión aparece correctamente para una marca sin salida de un día pasado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo: el filtro de fecha del panel de marcas muestra correctamente marcas fuera de la semana en curso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado por script directo: audit_log registra correctamente las acciones con actor y valores anterior/nuevo.</t>
   </si>
 </sst>
 </file>
@@ -1291,7 +1306,7 @@
         <v>154</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1337,7 +1352,7 @@
         <v>154</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1383,7 +1398,7 @@
         <v>154</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1521,7 +1536,7 @@
         <v>154</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1567,7 +1582,7 @@
         <v>154</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -623,6 +623,9 @@
   </si>
   <si>
     <t xml:space="preserve">Verificado por script directo: audit_log registra correctamente las acciones con actor y valores anterior/nuevo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se encontró y corrigió de raíz una condición de carrera real (rompía /admin/qr) moviendo la regeneración del QR a una función atómica en Postgres. Ver ESTADO_PRUEBAS.md. Falta reconfirmar en vivo.</t>
   </si>
 </sst>
 </file>
@@ -1559,7 +1562,7 @@
         <v>154</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -626,6 +626,9 @@
   </si>
   <si>
     <t xml:space="preserve">Se encontró y corrigió de raíz una condición de carrera real (rompía /admin/qr) moviendo la regeneración del QR a una función atómica en Postgres. Ver ESTADO_PRUEBAS.md. Falta reconfirmar en vivo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se encontró y corrigió de raíz una condición de carrera real (rompía /admin/qr) moviendo la regeneración del QR a una función atómica en Postgres. Confirmado en vivo: la página y el botón de regenerar funcionan correctamente.</t>
   </si>
 </sst>
 </file>
@@ -1562,7 +1565,7 @@
         <v>154</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="205">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -629,6 +629,18 @@
   </si>
   <si>
     <t xml:space="preserve">Se encontró y corrigió de raíz una condición de carrera real (rompía /admin/qr) moviendo la regeneración del QR a una función atómica en Postgres. Confirmado en vivo: la página y el botón de regenerar funcionan correctamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El dueño puede crear, editar y desactivar empleados. Al crear un empleado, debe ingresar: nombre completo, cédula, teléfono de contacto, mutualista, contacto de emergencia y correo electrónico (obligatorio, utilizado para el acceso y las comunicaciones del sistema), además de su cantidad de horas semanales pactadas, su valor hora nominal (obligatorio, usado para calcular la liquidación mensual) y un horario por defecto (días/horas), que se usará como base al configurar la semana en curso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo desde la app real: alta de empleado, generación de usuario e invitación por correo confirmadas. Se agregó el campo obligatorio "Valor hora nominal" (migración 0003_employee_hourly_rate.sql, ya aplicada a la base real). Falta reconfirmar en vivo el alta/edición con el campo nuevo — ver ESTADO_PRUEBAS.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El sistema genera un reporte descargable (Excel/PDF) por empleado y consolidado, con horas trabajadas, saldos semanales, ajustes manuales aplicados y totales del mes, listo para liquidación de haberes. Incluye el cálculo de la liquidación mensual (horas hasta las pactadas a valor simple, excedente pagado al doble, con las "horas extras que se están pagando" explícitas) y, en la hoja de cada empleado, un detalle diario de entrada/salida/horas trabajadas además del resumen semanal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo tras corregir el bug de semanas superpuestas: el reporte de julio ya muestra correctamente las horas trabajadas y el ajuste de Ana. Se agregó la liquidación mensual y el detalle diario por empleado (8 tests unitarios nuevos en monthly-math.test.ts); falta descargar un reporte real y confirmar visualmente ambas secciones nuevas. Ver ESTADO_PRUEBAS.md.</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1335,7 @@
         <v>35</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>36</v>
+        <v>201</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -1335,7 +1347,7 @@
         <v>154</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1507,7 +1519,7 @@
         <v>59</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>60</v>
+        <v>203</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>10</v>
@@ -1519,7 +1531,7 @@
         <v>154</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="206">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -641,6 +641,9 @@
   </si>
   <si>
     <t xml:space="preserve">Verificado en vivo tras corregir el bug de semanas superpuestas: el reporte de julio ya muestra correctamente las horas trabajadas y el ajuste de Ana. Se agregó la liquidación mensual y el detalle diario por empleado (8 tests unitarios nuevos en monthly-math.test.ts); falta descargar un reporte real y confirmar visualmente ambas secciones nuevas. Ver ESTADO_PRUEBAS.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/marcar activa la cámara (html5-qrcode), valida el QR contra el token activo y registra la marca en /api/time-entries/mark. Verificado en vivo en producción (Vercel, HTTPS): acceso a cámara y marcado real de entrada/salida desde el celular funcionando correctamente. Ver ESTADO_PRUEBAS.md.</t>
   </si>
 </sst>
 </file>
@@ -1232,7 +1235,7 @@
         <v>154</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -644,6 +644,9 @@
   </si>
   <si>
     <t xml:space="preserve">/marcar activa la cámara (html5-qrcode), valida el QR contra el token activo y registra la marca en /api/time-entries/mark. Verificado en vivo en producción (Vercel, HTTPS): acceso a cámara y marcado real de entrada/salida desde el celular funcionando correctamente. Ver ESTADO_PRUEBAS.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo desde la app real: alta de empleado, generación de usuario e invitación por correo confirmadas. Se agregó el campo obligatorio "Valor hora nominal" (migración 0003_employee_hourly_rate.sql, ya aplicada a la base real). El alta ahora también exige cargar el horario por defecto (RF-09) en el mismo formulario, validando que la suma de horas coincida exactamente con las horas semanales pactadas — si no coincide, se rechaza el alta con un mensaje explícito. Falta reconfirmar en vivo el alta con estos dos campos — ver ESTADO_PRUEBAS.md.</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1353,7 @@
         <v>154</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
+++ b/Backlog_Requerimientos_Control_Horario_Cafeteria.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="211">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -647,6 +647,18 @@
   </si>
   <si>
     <t xml:space="preserve">Verificado en vivo desde la app real: alta de empleado, generación de usuario e invitación por correo confirmadas. Se agregó el campo obligatorio "Valor hora nominal" (migración 0003_employee_hourly_rate.sql, ya aplicada a la base real). El alta ahora también exige cargar el horario por defecto (RF-09) en el mismo formulario, validando que la suma de horas coincida exactamente con las horas semanales pactadas — si no coincide, se rechaza el alta con un mensaje explícito. Falta reconfirmar en vivo el alta con estos dos campos — ver ESTADO_PRUEBAS.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El dueño puede crear, editar y desactivar empleados. Al crear un empleado, debe ingresar: nombre completo, cédula, teléfono de contacto, mutualista, contacto de emergencia y correo electrónico (obligatorio, utilizado para el acceso y las comunicaciones del sistema), además de sus horas semanales de contrato, sus horas semanales pactadas (pueden ser menores o mayores al contrato), su valor hora nominal (obligatorio, usado para calcular la liquidación mensual) y un horario por defecto (días/horas) que debe sumar exactamente las horas pactadas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo desde la app real: alta de empleado, generación de usuario e invitación por correo confirmadas. Se agregaron los campos obligatorios "Valor hora nominal" y "Horas semanales de contrato" (independiente de las pactadas), y el horario por defecto obligatorio validado contra las horas pactadas. Falta reconfirmar en vivo el campo de horas de contrato — ver ESTADO_PRUEBAS.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El sistema genera un reporte descargable (Excel) por empleado y consolidado, con horas trabajadas, saldos semanales, ajustes manuales aplicados y totales del mes, listo para liquidación de haberes. Incluye el cálculo de la liquidación mensual: las horas extra se calculan contra las horas de CONTRATO del empleado (no contra las pactadas, que pueden ser menores o mayores) — horas hasta el contrato a valor simple, excedente pagado al doble, con las "horas extras que se están pagando" explícitas. Cada hoja de empleado también tiene un detalle diario de entrada/salida/horas trabajadas además del resumen semanal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificado en vivo: reporte semanal/consolidado, liquidación con valor hora nominal y detalle diario confirmados. Se redefinió el cálculo de horas extra para que se midan contra las horas de contrato (no las pactadas) — nuevo test en monthly-math.test.ts; falta descargar un reporte real y confirmar visualmente el cambio. Ver ESTADO_PRUEBAS.md.</t>
   </si>
 </sst>
 </file>
@@ -1341,7 +1353,7 @@
         <v>35</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -1353,7 +1365,7 @@
         <v>154</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1525,7 +1537,7 @@
         <v>59</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>10</v>
@@ -1537,7 +1549,7 @@
         <v>154</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
